--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-18.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-18.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988310016</v>
+        <v>5521967363838</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arianny</t>
+          <t>Francinaldo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arianny Nunes C Figueiredo</t>
+          <t>Francinaldo Fernandes dos Santos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5511959187091</v>
+        <v>5583993214959</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rijoze</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rijoze Barbosa da Silva</t>
+          <t>Maria das Gracas Barbosa de Moura</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988031804</v>
+        <v>5583987561090</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Companhia</t>
+          <t>Tania</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Companhia de Agua e Esgotos da Paraiba Cagepa</t>
+          <t>Tania Maria da Silva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987168330</v>
+        <v>5583993345205</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ivanile</t>
+          <t>Edvandro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ivanile de Oliveira Ribeiro</t>
+          <t>Edvandro Araujo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583988010582</v>
+        <v>5583981674469</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adelson</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adelson Ferreira Pereira Junior</t>
+          <t>Tiago Santos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583986170641</v>
+        <v>5511973220000</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rebeca</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rebeca de Lima Borges</t>
+          <t>Sergio Namur</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583986434400</v>
+        <v>5583991311521</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Humberto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maria Niedja Job Monteiro</t>
+          <t>Humberto Cardoso</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988895839</v>
+        <v>5583996722636</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lucia</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lucia de Oliveira</t>
+          <t>Jose Humberth Pereira</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583986102201</v>
+        <v>5583986401948</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manoel Rodrigues da Silva</t>
+          <t>Camila de Medeiros Dantas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583986203181</v>
+        <v>5583999393622</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Expedito</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Expedito Alves Texeira</t>
+          <t>Joao Batista de Sousa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583998635448</v>
+        <v>5583991662277</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maria da Guia e Silva</t>
+          <t>Lucas Marciel de Castro Silva</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583986693024</v>
+        <v>5583991577535</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mercia</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mercia Michele Araújo Honorio</t>
+          <t>Carlos Antonio da Silva</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583988600008</v>
+        <v>5583988891862</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oca</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oca Restaurante</t>
+          <t>Christian Oliveira de Lucena</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583996857723</v>
+        <v>5583988310016</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portobello</t>
+          <t>Arianny</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portobello Shop</t>
+          <t>Arianny Nunes C Figueiredo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583987953766</v>
+        <v>5511959187091</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rosete</t>
+          <t>Rijoze</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rosete Coelho Barbosa</t>
+          <t>Rijoze Barbosa da Silva</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988069200</v>
+        <v>5583988031804</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Danillo</t>
+          <t>Companhia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Danillo Souza de Paiva</t>
+          <t>Companhia de Agua e Esgotos da Paraiba Cagepa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583987526151</v>
+        <v>5583987168330</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oseias</t>
+          <t>Ivanile</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oseias Abdon da Silva</t>
+          <t>Ivanile de Oliveira Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583991526974</v>
+        <v>5583988010582</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Joellington</t>
+          <t>Adelson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joellington Alves Barbosa</t>
+          <t>Adelson Ferreira Pereira Junior</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987299791</v>
+        <v>5583986170641</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Andry</t>
+          <t>Rebeca</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Andry Gabriel</t>
+          <t>Rebeca de Lima Borges</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988913050</v>
+        <v>5583986434400</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luciano</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luciano Carvalho da Silva</t>
+          <t>Maria Niedja Job Monteiro</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583986111008</v>
+        <v>5583988895839</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Lucia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paulo Rogerio Araujo</t>
+          <t>Lucia de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5585981817969</v>
+        <v>5583986102201</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ventura</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ventura Telecom</t>
+          <t>Manoel Rodrigues da Silva</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583991485488</v>
+        <v>5583986203181</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arnaldo</t>
+          <t>Expedito</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arnaldo Romanus</t>
+          <t>Expedito Alves Texeira</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583999469440</v>
+        <v>5583998635448</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rafael Pereira Gomes</t>
+          <t>Maria da Guia e Silva</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583999390711</v>
+        <v>5583986693024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Mercia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rita de Cassia Macedo Diniz</t>
+          <t>Mercia Michele Araújo Honorio</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583988556912</v>
+        <v>5583988600008</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Oca</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Araujo de Lacerda</t>
+          <t>Oca Restaurante</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583999029177</v>
+        <v>5583996857723</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adelmo</t>
+          <t>Portobello</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adelmo Justino da Silva</t>
+          <t>Portobello Shop</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583988149215</v>
+        <v>5583987953766</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Edileusa</t>
+          <t>Rosete</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edileusa de Medeiros Viana</t>
+          <t>Rosete Coelho Barbosa</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583996388053</v>
+        <v>5583988069200</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cristiano</t>
+          <t>Danillo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cristiano Freitas Lins Mesquita</t>
+          <t>Danillo Souza de Paiva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5511996014654</v>
+        <v>5583987526151</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adao</t>
+          <t>Oseias</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Adao de Paula Ferreira</t>
+          <t>Oseias Abdon da Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583986332663</v>
+        <v>5583991526974</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Carlito</t>
+          <t>Joellington</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carlito Fernandes Alves</t>
+          <t>Joellington Alves Barbosa</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583986040579</v>
+        <v>5583987299791</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Valmir</t>
+          <t>Andry</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valmir Gomes da Silva</t>
+          <t>Andry Gabriel</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583998441080</v>
+        <v>5583988913050</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lafesta</t>
+          <t>Luciano</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lafesta</t>
+          <t>Luciano Carvalho da Silva</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5521986422927</v>
+        <v>5583986111008</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marinaldo</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Marinaldo Antonio da Silva</t>
+          <t>Paulo Rogerio Araujo</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583988033696</v>
+        <v>5585981817969</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Josivaldo</t>
+          <t>Ventura</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Josivaldo Severino Gomes</t>
+          <t>Ventura Telecom</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583983389405</v>
+        <v>5583991485488</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Arnaldo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ana Lucia dos Santos Silva</t>
+          <t>Arnaldo Romanus</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583998533337</v>
+        <v>5583999469440</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Edinaldo</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Edinaldo Santos de Andrade</t>
+          <t>Rafael Pereira Gomes</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583986292098</v>
+        <v>5583999390711</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Claudenice</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Claudenice Pereira Mendes</t>
+          <t>Rita de Cassia Macedo Diniz</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583998464502</v>
+        <v>5583988556912</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gean</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gean Carlos de Sousa Queiroz Freire</t>
+          <t>Carlos Eduardo Araujo de Lacerda</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583981687726</v>
+        <v>5583999029177</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Adelmo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maria Vitória</t>
+          <t>Adelmo Justino da Silva</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583999886965</v>
+        <v>5583988149215</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Edileusa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ana Clara Mendes Leite</t>
+          <t>Edileusa de Medeiros Viana</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583991679589</v>
+        <v>5583996388053</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>Cristiano</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Matheus Andrade Rodrigues</t>
+          <t>Cristiano Freitas Lins Mesquita</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5511954995387</v>
+        <v>5511996014654</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Adao</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jose Ivanildo Martins Fernandes</t>
+          <t>Adao de Paula Ferreira</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583986122161</v>
+        <v>5517999161886</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jose Lins Bezerra</t>
+          <t>Joao Henrique dos Reis Barreto</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583996193565</v>
+        <v>5583986332663</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Semas</t>
+          <t>Carlito</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semas</t>
+          <t>Carlito Fernandes Alves</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988741407</v>
+        <v>5583986040579</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ariana</t>
+          <t>Valmir</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ariana Batista Leite</t>
+          <t>Valmir Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583998573498</v>
+        <v>5583998441080</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aaoml</t>
+          <t>Lafesta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Aaoml</t>
+          <t>Lafesta</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583996816746</v>
+        <v>5521986422927</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Geoliana</t>
+          <t>Marinaldo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Geoliana Nobrega</t>
+          <t>Marinaldo Antonio da Silva</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583999466313</v>
+        <v>5583988033696</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Josivaldo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jorge Ramos da Silva</t>
+          <t>Josivaldo Severino Gomes</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583999134287</v>
+        <v>5583983389405</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lucas da Silva Alves</t>
+          <t>Ana Lucia dos Santos Silva</t>
         </is>
       </c>
     </row>
